--- a/lab4/I142113.xlsx
+++ b/lab4/I142113.xlsx
@@ -8,14 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/magdalenasmietana/Documents/Fizyka/Fizyka-Lab/lab4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1CE17F3-87F9-D54B-8D0C-3FA38C3CDE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6584A196-43AE-CB4B-BE89-25967B59F604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16680" xr2:uid="{57187E8D-46F6-554C-8982-2CC030F76FF2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{57187E8D-46F6-554C-8982-2CC030F76FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$O$5:$O$50</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$P$5:$P$50</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$O$4:$O$50</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$P$4</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$P$5:$P$50</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$O$5:$O$50</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$P$5:$P$50</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$O$5:$O$50</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$P$5:$P$50</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$O$5:$O$50</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$P$5:$P$50</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$O$5:$O$50</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$P$5:$P$50</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,12 +50,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Ciśnienie [hPa]</t>
-  </si>
-  <si>
-    <t>Opór [Ω]</t>
   </si>
   <si>
     <t>Temperatura [K]</t>
@@ -48,11 +60,47 @@
   <si>
     <t>Pomiary temperatury w zależności od ciśnienia.</t>
   </si>
+  <si>
+    <t>Opór [Ω] - pomiar 1</t>
+  </si>
+  <si>
+    <t>Opór [Ω] - pomiar 2</t>
+  </si>
+  <si>
+    <t>h1</t>
+  </si>
+  <si>
+    <t>130 mm</t>
+  </si>
+  <si>
+    <t>h2</t>
+  </si>
+  <si>
+    <t>80 mm</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>4.04 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opór [Ω] </t>
+  </si>
+  <si>
+    <t>cisnienie [hPa]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opór średni [Ω] </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -90,9 +138,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -108,6 +157,1270 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="105"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="5"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Pomiary temperatury w zależności od ciśnienia.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$O$5:$O$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>-1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-950</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-900</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-850</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-750</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-650</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-600</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-550</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-450</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-400</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-350</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-300</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-250</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-200</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-150</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1150</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1300</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$P$5:$P$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>61.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>63.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>68.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>71.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>72.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>73.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>74.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>74.8</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>75.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>76.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>77.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>77.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>78.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>78.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>79.3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>79.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>80.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>80.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>80.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>81.2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>81.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>81.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>82.1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>82.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>82.8</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>83.1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>83.3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>83.5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>83.8</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>84.5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>84.7</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>84.9</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>85.2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>85.6</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>86.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AC99-7640-B9E2-332225E009CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1908479231"/>
+        <c:axId val="1903962623"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1908479231"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1400"/>
+          <c:min val="-1100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Ciśnienie [hPa]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1903962623"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1903962623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="60"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Temperatura [K]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1908479231"/>
+        <c:crossesAt val="-1500"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+  <a:schemeClr val="accent3"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228601</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>135467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>177801</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C26832BD-B1E2-C52B-9B4A-6CEDCA09E853}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -407,255 +1720,1046 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F1C0FF-61BA-5A4B-B3C0-624E87EF0EDB}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3">
+        <v>20.34</v>
+      </c>
+      <c r="C3">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="D3" s="2">
+        <f>AVERAGE(B3,C3)</f>
+        <v>20.380000000000003</v>
+      </c>
+      <c r="E3">
+        <v>77.7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>20.5</v>
+      </c>
+      <c r="C4">
+        <v>20.58</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D29" si="0">AVERAGE(B4,C4)</f>
+        <v>20.54</v>
+      </c>
+      <c r="E4">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="G4">
+        <v>-1000</v>
+      </c>
+      <c r="H4" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="I4">
+        <v>61.9</v>
+      </c>
+      <c r="O4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="B5">
+        <v>20.7</v>
+      </c>
+      <c r="C5">
+        <v>20.75</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>20.725000000000001</v>
+      </c>
+      <c r="E5">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G5">
+        <v>-950</v>
+      </c>
+      <c r="H5" s="2">
+        <v>14.21</v>
+      </c>
+      <c r="I5">
+        <v>62.8</v>
+      </c>
+      <c r="O5">
+        <v>-1000</v>
+      </c>
+      <c r="P5">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>150</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="B6">
+        <v>20.87</v>
+      </c>
+      <c r="C6">
+        <v>20.92</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>20.895000000000003</v>
+      </c>
+      <c r="E6">
+        <v>78.8</v>
+      </c>
+      <c r="G6">
+        <v>-900</v>
+      </c>
+      <c r="H6" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="I6">
+        <v>63.8</v>
+      </c>
+      <c r="O6">
+        <v>-950</v>
+      </c>
+      <c r="P6">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>200</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="B7">
+        <v>21.05</v>
+      </c>
+      <c r="C7">
+        <v>21.1</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>21.075000000000003</v>
+      </c>
+      <c r="E7">
+        <v>79.3</v>
+      </c>
+      <c r="G7">
+        <v>-850</v>
+      </c>
+      <c r="H7" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="I7">
+        <v>65.8</v>
+      </c>
+      <c r="O7">
+        <v>-900</v>
+      </c>
+      <c r="P7">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>250</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="B8">
+        <v>21.22</v>
+      </c>
+      <c r="C8">
+        <v>21.25</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>21.234999999999999</v>
+      </c>
+      <c r="E8">
+        <v>79.5</v>
+      </c>
+      <c r="G8">
+        <v>-800</v>
+      </c>
+      <c r="H8" s="2">
+        <v>16.02</v>
+      </c>
+      <c r="I8">
+        <v>67.2</v>
+      </c>
+      <c r="O8">
+        <v>-850</v>
+      </c>
+      <c r="P8">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="B9">
+        <v>21.36</v>
+      </c>
+      <c r="C9">
+        <v>21.38</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>21.369999999999997</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>-750</v>
+      </c>
+      <c r="H9" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="I9">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="K9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9">
+        <v>-800</v>
+      </c>
+      <c r="P9">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>350</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="B10">
+        <v>21.36</v>
+      </c>
+      <c r="C10">
+        <v>21.58</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>21.47</v>
+      </c>
+      <c r="E10">
+        <v>80.5</v>
+      </c>
+      <c r="G10">
+        <v>-700</v>
+      </c>
+      <c r="H10" s="2">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="I10">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="K10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10">
+        <v>-750</v>
+      </c>
+      <c r="P10">
+        <v>68.400000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>400</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="B11">
+        <v>21.64</v>
+      </c>
+      <c r="C11">
+        <v>21.65</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>21.645</v>
+      </c>
+      <c r="E11">
+        <v>80.5</v>
+      </c>
+      <c r="G11">
+        <v>-650</v>
+      </c>
+      <c r="H11" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="I11">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="K11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>-700</v>
+      </c>
+      <c r="P11">
+        <v>69.400000000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>450</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="B12">
+        <v>21.76</v>
+      </c>
+      <c r="C12">
+        <v>21.7</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>21.73</v>
+      </c>
+      <c r="E12">
+        <v>80.7</v>
+      </c>
+      <c r="G12">
+        <v>-600</v>
+      </c>
+      <c r="H12" s="2">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="I12">
+        <v>71.3</v>
+      </c>
+      <c r="O12">
+        <v>-650</v>
+      </c>
+      <c r="P12">
+        <v>70.599999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>500</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="B13">
+        <v>21.92</v>
+      </c>
+      <c r="C13">
+        <v>21.86</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>21.89</v>
+      </c>
+      <c r="E13">
+        <v>81.2</v>
+      </c>
+      <c r="G13">
+        <v>-550</v>
+      </c>
+      <c r="H13" s="2">
+        <v>18</v>
+      </c>
+      <c r="I13">
+        <v>72</v>
+      </c>
+      <c r="O13">
+        <v>-600</v>
+      </c>
+      <c r="P13">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>550</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="B14">
+        <v>22.06</v>
+      </c>
+      <c r="C14">
+        <v>21.98</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>22.02</v>
+      </c>
+      <c r="E14">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="G14">
+        <v>-500</v>
+      </c>
+      <c r="H14" s="2">
+        <v>18.25</v>
+      </c>
+      <c r="I14">
+        <v>72.7</v>
+      </c>
+      <c r="O14">
+        <v>-550</v>
+      </c>
+      <c r="P14">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>600</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="B15">
+        <v>22.2</v>
+      </c>
+      <c r="C15">
+        <v>22.13</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>22.164999999999999</v>
+      </c>
+      <c r="E15">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="G15">
+        <v>-450</v>
+      </c>
+      <c r="H15" s="2">
+        <v>18.54</v>
+      </c>
+      <c r="I15">
+        <v>73.2</v>
+      </c>
+      <c r="O15">
+        <v>-500</v>
+      </c>
+      <c r="P15">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>650</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="B16">
+        <v>22.33</v>
+      </c>
+      <c r="C16">
+        <v>22.2</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>22.265000000000001</v>
+      </c>
+      <c r="E16">
+        <v>82.1</v>
+      </c>
+      <c r="G16">
+        <v>-400</v>
+      </c>
+      <c r="H16" s="2">
+        <v>18.77</v>
+      </c>
+      <c r="I16">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="O16">
+        <v>-450</v>
+      </c>
+      <c r="P16">
+        <v>73.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>700</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="B17">
+        <v>22.45</v>
+      </c>
+      <c r="C17">
+        <v>22.35</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>22.4</v>
+      </c>
+      <c r="E17">
+        <v>82.4</v>
+      </c>
+      <c r="G17">
+        <v>-350</v>
+      </c>
+      <c r="H17" s="2">
+        <v>19</v>
+      </c>
+      <c r="I17">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="O17">
+        <v>-400</v>
+      </c>
+      <c r="P17">
+        <v>73.900000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>750</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="B18">
+        <v>22.6</v>
+      </c>
+      <c r="C18">
+        <v>22.5</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>22.55</v>
+      </c>
+      <c r="E18">
+        <v>82.8</v>
+      </c>
+      <c r="G18">
+        <v>-300</v>
+      </c>
+      <c r="H18" s="2">
+        <v>19.22</v>
+      </c>
+      <c r="I18">
+        <v>74.8</v>
+      </c>
+      <c r="O18">
+        <v>-350</v>
+      </c>
+      <c r="P18">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>800</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="B19">
+        <v>22.72</v>
+      </c>
+      <c r="C19">
+        <v>22.6</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>22.66</v>
+      </c>
+      <c r="E19">
+        <v>83.1</v>
+      </c>
+      <c r="G19">
+        <v>-250</v>
+      </c>
+      <c r="H19" s="2">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="I19">
+        <v>75.5</v>
+      </c>
+      <c r="O19">
+        <v>-300</v>
+      </c>
+      <c r="P19">
+        <v>74.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>850</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18">
+      <c r="B20">
+        <v>22.81</v>
+      </c>
+      <c r="C20">
+        <v>22.72</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="0"/>
+        <v>22.765000000000001</v>
+      </c>
+      <c r="E20">
+        <v>83.3</v>
+      </c>
+      <c r="G20">
+        <v>-200</v>
+      </c>
+      <c r="H20" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="I20">
+        <v>76</v>
+      </c>
+      <c r="O20">
+        <v>-250</v>
+      </c>
+      <c r="P20">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>900</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="B21">
+        <v>22.93</v>
+      </c>
+      <c r="C21">
+        <v>22.85</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="0"/>
+        <v>22.89</v>
+      </c>
+      <c r="E21">
+        <v>83.5</v>
+      </c>
+      <c r="G21">
+        <v>-150</v>
+      </c>
+      <c r="H21" s="2">
+        <v>19.88</v>
+      </c>
+      <c r="I21">
+        <v>76.5</v>
+      </c>
+      <c r="O21">
+        <v>-200</v>
+      </c>
+      <c r="P21">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>950</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="B22">
+        <v>22.98</v>
+      </c>
+      <c r="C22">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>22.990000000000002</v>
+      </c>
+      <c r="E22">
+        <v>83.8</v>
+      </c>
+      <c r="G22">
+        <v>-100</v>
+      </c>
+      <c r="H22" s="2">
+        <v>20.05</v>
+      </c>
+      <c r="I22">
+        <v>77</v>
+      </c>
+      <c r="O22">
+        <v>-150</v>
+      </c>
+      <c r="P22">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>1000</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="B23">
+        <v>23.15</v>
+      </c>
+      <c r="C23">
+        <v>23.11</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>23.13</v>
+      </c>
+      <c r="E23">
+        <v>84</v>
+      </c>
+      <c r="O23">
+        <v>-100</v>
+      </c>
+      <c r="P23">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>1050</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="B24">
+        <v>23.25</v>
+      </c>
+      <c r="C24">
+        <v>23.28</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>23.265000000000001</v>
+      </c>
+      <c r="E24">
+        <v>84.5</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>1100</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="B25">
+        <v>23.35</v>
+      </c>
+      <c r="C25">
+        <v>23.42</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>23.385000000000002</v>
+      </c>
+      <c r="E25">
+        <v>84.7</v>
+      </c>
+      <c r="O25">
+        <v>50</v>
+      </c>
+      <c r="P25">
+        <v>77.900000000000006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>1150</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="B26">
+        <v>23.47</v>
+      </c>
+      <c r="C26">
+        <v>23.5</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>23.484999999999999</v>
+      </c>
+      <c r="E26">
+        <v>84.9</v>
+      </c>
+      <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>1200</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="B27">
+        <v>23.63</v>
+      </c>
+      <c r="C27">
+        <v>23.63</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="0"/>
+        <v>23.63</v>
+      </c>
+      <c r="E27">
+        <v>85.2</v>
+      </c>
+      <c r="O27">
+        <v>150</v>
+      </c>
+      <c r="P27">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>1250</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="C28">
+        <v>23.78</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="0"/>
+        <v>23.78</v>
+      </c>
+      <c r="E28">
+        <v>85.6</v>
+      </c>
+      <c r="O28">
+        <v>200</v>
+      </c>
+      <c r="P28">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>1300</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>2300</v>
+      <c r="C29">
+        <v>24.16</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="0"/>
+        <v>24.16</v>
+      </c>
+      <c r="E29">
+        <v>86.6</v>
+      </c>
+      <c r="O29">
+        <v>250</v>
+      </c>
+      <c r="P29">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O30">
+        <v>300</v>
+      </c>
+      <c r="P30">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O31">
+        <v>350</v>
+      </c>
+      <c r="P31">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O32">
+        <v>400</v>
+      </c>
+      <c r="P32">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="33" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O33">
+        <v>450</v>
+      </c>
+      <c r="P33">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="34" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O34">
+        <v>500</v>
+      </c>
+      <c r="P34">
+        <v>81.2</v>
+      </c>
+    </row>
+    <row r="35" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O35">
+        <v>550</v>
+      </c>
+      <c r="P35">
+        <v>81.400000000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O36">
+        <v>600</v>
+      </c>
+      <c r="P36">
+        <v>81.900000000000006</v>
+      </c>
+    </row>
+    <row r="37" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O37">
+        <v>650</v>
+      </c>
+      <c r="P37">
+        <v>82.1</v>
+      </c>
+    </row>
+    <row r="38" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O38">
+        <v>700</v>
+      </c>
+      <c r="P38">
+        <v>82.4</v>
+      </c>
+    </row>
+    <row r="39" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O39">
+        <v>750</v>
+      </c>
+      <c r="P39">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="40" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O40">
+        <v>800</v>
+      </c>
+      <c r="P40">
+        <v>83.1</v>
+      </c>
+    </row>
+    <row r="41" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O41">
+        <v>850</v>
+      </c>
+      <c r="P41">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="42" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O42">
+        <v>900</v>
+      </c>
+      <c r="P42">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="43" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O43">
+        <v>950</v>
+      </c>
+      <c r="P43">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="44" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O44">
+        <v>1000</v>
+      </c>
+      <c r="P44">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O45">
+        <v>1050</v>
+      </c>
+      <c r="P45">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="46" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O46">
+        <v>1100</v>
+      </c>
+      <c r="P46">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="47" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O47">
+        <v>1150</v>
+      </c>
+      <c r="P47">
+        <v>84.9</v>
+      </c>
+    </row>
+    <row r="48" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O48">
+        <v>1200</v>
+      </c>
+      <c r="P48">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="49" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O49">
+        <v>1250</v>
+      </c>
+      <c r="P49">
+        <v>85.6</v>
+      </c>
+    </row>
+    <row r="50" spans="15:16" x14ac:dyDescent="0.2">
+      <c r="O50">
+        <v>1300</v>
+      </c>
+      <c r="P50">
+        <v>86.6</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G4:I22">
+    <sortCondition ref="G4:G22"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>